--- a/artfynd/A 25776-2024 artfynd.xlsx
+++ b/artfynd/A 25776-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122528662</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>100049</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 25776-2024 artfynd.xlsx
+++ b/artfynd/A 25776-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122528662</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 25776-2024 artfynd.xlsx
+++ b/artfynd/A 25776-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,6 +790,124 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125111978</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57847</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hagbacken, Ålefors, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>538819</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6354918</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25776-2024 artfynd.xlsx
+++ b/artfynd/A 25776-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>125111978</v>
       </c>
       <c r="B3" t="n">
-        <v>57847</v>
+        <v>57961</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 25776-2024 artfynd.xlsx
+++ b/artfynd/A 25776-2024 artfynd.xlsx
@@ -796,12 +796,7 @@
         <v>125111978</v>
       </c>
       <c r="B3" t="n">
-        <v>57961</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25776-2024 artfynd.xlsx
+++ b/artfynd/A 25776-2024 artfynd.xlsx
@@ -678,7 +678,12 @@
         <v>122528662</v>
       </c>
       <c r="B2" t="n">
-        <v>57881</v>
+        <v>57494</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25776-2024 artfynd.xlsx
+++ b/artfynd/A 25776-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122528662</v>
+        <v>122981837</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,13 +705,13 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -731,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538828</v>
+        <v>538809</v>
       </c>
       <c r="R2" t="n">
-        <v>6354939</v>
+        <v>6354950</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,12 +756,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,27 +793,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125111978</v>
+        <v>122528662</v>
       </c>
       <c r="B3" t="n">
-        <v>57979</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103008</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,18 +823,18 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538819</v>
+        <v>538828</v>
       </c>
       <c r="R3" t="n">
-        <v>6354918</v>
+        <v>6354939</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,12 +874,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134314145</v>
+        <v>99548554</v>
       </c>
       <c r="B4" t="n">
-        <v>58349</v>
+        <v>58286</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,16 +917,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -936,31 +936,31 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hagbacken, Ålefors, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538845</v>
+        <v>538790</v>
       </c>
       <c r="R4" t="n">
-        <v>6354922</v>
+        <v>6354951</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,12 +987,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,6 +1016,567 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125111978</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58286</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hagbacken, Ålefors, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>538819</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6354918</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>86731419</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Blackelid, Ålefors, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>538793</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6354915</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-07-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-07-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>92124577</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hagbacken, Ålefors, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>538822</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6354965</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-04-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-04-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134314145</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hagbacken, Ålefors, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>538845</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6354922</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122979260</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hagbacken, Ålefors, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>538809</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6354950</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25776-2024 artfynd.xlsx
+++ b/artfynd/A 25776-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122981837</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122528662</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99548554</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125111978</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86731419</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1355,6 +1385,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92124577</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1468,6 +1503,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134314145</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1577,8 +1617,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122979260</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>